--- a/artfynd/A 34814-2024 artfynd.xlsx
+++ b/artfynd/A 34814-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119785770</v>
+        <v>119785628</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599096</v>
+        <v>599249</v>
       </c>
       <c r="R2" t="n">
-        <v>7045796</v>
+        <v>7045795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119785628</v>
+        <v>119785770</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599249</v>
+        <v>599096</v>
       </c>
       <c r="R3" t="n">
-        <v>7045795</v>
+        <v>7045796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34814-2024 artfynd.xlsx
+++ b/artfynd/A 34814-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119785628</v>
+        <v>119785770</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599249</v>
+        <v>599096</v>
       </c>
       <c r="R2" t="n">
-        <v>7045795</v>
+        <v>7045796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119785770</v>
+        <v>119785628</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599096</v>
+        <v>599249</v>
       </c>
       <c r="R3" t="n">
-        <v>7045796</v>
+        <v>7045795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34814-2024 artfynd.xlsx
+++ b/artfynd/A 34814-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119785770</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>119785628</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34814-2024 artfynd.xlsx
+++ b/artfynd/A 34814-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119785770</v>
+        <v>119785628</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599096</v>
+        <v>599249</v>
       </c>
       <c r="R2" t="n">
-        <v>7045796</v>
+        <v>7045795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119785628</v>
+        <v>119785770</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599249</v>
+        <v>599096</v>
       </c>
       <c r="R3" t="n">
-        <v>7045795</v>
+        <v>7045796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
